--- a/TextGame project/Assets/Resources/Story/6.xlsx
+++ b/TextGame project/Assets/Resources/Story/6.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBBDC0DD-B07B-4099-AB46-AB44269CB179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/TextGame project/Assets/Resources/Story/6.xlsx
+++ b/TextGame project/Assets/Resources/Story/6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBBDC0DD-B07B-4099-AB46-AB44269CB179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B90A16-7661-453F-809A-B4F9C7436969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,9 +128,6 @@
     <t>千叶</t>
   </si>
   <si>
-    <t>Qianye</t>
-  </si>
-  <si>
     <t>（那个人走到他们刚才待的地方，停了下来）</t>
   </si>
   <si>
@@ -329,6 +326,10 @@
   </si>
   <si>
     <t>（小声，带着哭腔）走、走了吗...</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye2</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -981,7 +982,7 @@
     </row>
     <row r="2" spans="1:22">
       <c r="G2" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H2">
         <v>3</v>
@@ -1004,25 +1005,25 @@
         <v>2</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J3" s="5">
         <v>-640.83010000000002</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>31</v>
+      <c r="K3" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M3" s="5">
         <v>819.16989999999998</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -1114,19 +1115,19 @@
         <v>24</v>
       </c>
       <c r="I7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="P7" s="5">
+        <v>570</v>
+      </c>
+      <c r="Q7" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="P7" s="5">
-        <v>570</v>
-      </c>
-      <c r="Q7" s="7" t="s">
-        <v>71</v>
       </c>
       <c r="R7">
         <v>6</v>
@@ -1175,10 +1176,10 @@
         <v>30</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
+        <v>71</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="R9">
         <v>6</v>
@@ -1201,7 +1202,7 @@
         <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
         <v>24</v>
@@ -1227,7 +1228,7 @@
         <v>22</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
@@ -1253,7 +1254,7 @@
         <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
         <v>24</v>
@@ -1279,7 +1280,7 @@
         <v>22</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
         <v>24</v>
@@ -1305,7 +1306,7 @@
         <v>22</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
         <v>24</v>
@@ -1331,7 +1332,7 @@
         <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
         <v>24</v>
@@ -1357,7 +1358,7 @@
         <v>22</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
         <v>24</v>
@@ -1380,13 +1381,13 @@
     </row>
     <row r="17" spans="1:22">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R17">
         <v>6</v>
@@ -1409,7 +1410,7 @@
         <v>22</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
         <v>24</v>
@@ -1435,10 +1436,10 @@
         <v>30</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>31</v>
+        <v>73</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="R19">
         <v>6</v>
@@ -1461,28 +1462,28 @@
         <v>22</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
         <v>24</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J20" s="5">
         <v>-640.83010000000002</v>
       </c>
-      <c r="K20" s="5" t="s">
-        <v>31</v>
+      <c r="K20" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M20" s="5">
         <v>819.16989999999998</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R20">
         <v>6</v>
@@ -1502,13 +1503,13 @@
     </row>
     <row r="21" spans="1:22">
       <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s">
         <v>42</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>43</v>
       </c>
       <c r="R21">
         <v>6</v>
@@ -1531,7 +1532,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
         <v>24</v>
@@ -1557,13 +1558,13 @@
     </row>
     <row r="23" spans="1:22">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R23">
         <v>6</v>
@@ -1586,7 +1587,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
         <v>24</v>
@@ -1612,7 +1613,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
         <v>24</v>
@@ -1641,10 +1642,10 @@
         <v>30</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" t="s">
-        <v>31</v>
+        <v>76</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="R26">
         <v>4</v>
@@ -1664,13 +1665,13 @@
     </row>
     <row r="27" spans="1:22">
       <c r="A27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" t="s">
         <v>42</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" t="s">
-        <v>43</v>
       </c>
       <c r="R27">
         <v>4</v>
@@ -1693,7 +1694,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
         <v>24</v>
@@ -1719,7 +1720,7 @@
         <v>22</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
         <v>24</v>
@@ -1745,10 +1746,10 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" t="s">
-        <v>31</v>
+        <v>78</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="R30">
         <v>4</v>
@@ -1768,13 +1769,13 @@
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" t="s">
         <v>42</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" t="s">
-        <v>43</v>
       </c>
       <c r="R31">
         <v>4</v>
@@ -1797,10 +1798,10 @@
         <v>30</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" t="s">
-        <v>31</v>
+        <v>80</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="R32">
         <v>4</v>
@@ -1823,7 +1824,7 @@
         <v>22</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
         <v>24</v>
@@ -1846,13 +1847,13 @@
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" t="s">
         <v>42</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" t="s">
-        <v>43</v>
       </c>
       <c r="R34">
         <v>4</v>
@@ -1875,10 +1876,10 @@
         <v>30</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" t="s">
-        <v>31</v>
+        <v>82</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="R35">
         <v>4</v>
@@ -1898,13 +1899,13 @@
     </row>
     <row r="36" spans="1:22">
       <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" t="s">
         <v>42</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" t="s">
-        <v>43</v>
       </c>
       <c r="R36">
         <v>4</v>
@@ -1927,10 +1928,10 @@
         <v>30</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" t="s">
-        <v>31</v>
+        <v>84</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="R37">
         <v>4</v>
@@ -1950,13 +1951,13 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" t="s">
         <v>42</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C38" t="s">
-        <v>43</v>
       </c>
       <c r="R38">
         <v>4</v>
@@ -1979,13 +1980,13 @@
         <v>22</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
         <v>24</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R39">
         <v>4</v>
@@ -2008,7 +2009,7 @@
         <v>22</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" t="s">
         <v>24</v>
@@ -2034,7 +2035,7 @@
         <v>22</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C41" t="s">
         <v>24</v>
@@ -2060,10 +2061,10 @@
         <v>30</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C42" t="s">
-        <v>31</v>
+        <v>86</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="R42">
         <v>4</v>
@@ -2086,7 +2087,7 @@
         <v>22</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
         <v>24</v>
@@ -2112,7 +2113,7 @@
         <v>22</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44" t="s">
         <v>24</v>
@@ -2141,7 +2142,7 @@
         <v>22</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45" t="s">
         <v>24</v>
@@ -2167,7 +2168,7 @@
         <v>22</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46" t="s">
         <v>24</v>
@@ -2190,13 +2191,13 @@
     </row>
     <row r="47" spans="1:22">
       <c r="A47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R47" s="6">
         <v>7</v>
@@ -2219,7 +2220,7 @@
         <v>22</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C48" t="s">
         <v>24</v>
@@ -2242,13 +2243,13 @@
     </row>
     <row r="49" spans="1:22">
       <c r="A49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R49" s="6">
         <v>7</v>
@@ -2271,7 +2272,7 @@
         <v>22</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C50" t="s">
         <v>24</v>
@@ -2297,10 +2298,10 @@
         <v>30</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C51" t="s">
-        <v>31</v>
+        <v>89</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="R51" s="6">
         <v>7</v>
@@ -2323,7 +2324,7 @@
         <v>22</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C52" t="s">
         <v>24</v>
@@ -2349,7 +2350,7 @@
         <v>22</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C53" t="s">
         <v>24</v>
@@ -2375,7 +2376,7 @@
         <v>22</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C54" t="s">
         <v>24</v>
@@ -2401,13 +2402,13 @@
         <v>22</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C55" t="s">
         <v>24</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R55" s="6">
         <v>7</v>
@@ -2430,7 +2431,7 @@
         <v>22</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C56" t="s">
         <v>24</v>
@@ -2456,7 +2457,7 @@
         <v>22</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C57" t="s">
         <v>24</v>
@@ -2482,10 +2483,10 @@
         <v>30</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="C58" t="s">
-        <v>31</v>
       </c>
       <c r="R58" s="6">
         <v>7</v>
@@ -2508,7 +2509,7 @@
         <v>22</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C59" t="s">
         <v>24</v>
@@ -2531,16 +2532,16 @@
     </row>
     <row r="60" spans="1:22">
       <c r="A60" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="C60">
         <v>7</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E60">
         <v>8</v>
@@ -2552,7 +2553,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A59 A61:A176" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"千叶,旁白,林深,神秘人"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C61:C161 C3:C16 C18:C22 C24:C46 C48 C50:C59" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C61:C161 C43:C46 C10:C16 C20:C22 C48 C3:C8 C18 C24:C25 C27:C29 C31 C33:C34 C36 C38:C41 C50 C52:C57 C59" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Qianye,White,Linshen"</formula1>
     </dataValidation>
   </dataValidations>
